--- a/Excel/LookupFunctions1.xlsx
+++ b/Excel/LookupFunctions1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D0FB42-E1BE-4679-8C4F-005035FE1AF1}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E569756-895D-49A0-BC3A-000608E84A59}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="1" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
     <sheet name="Vlookup" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RawData!$A$1:$AI$85</definedName>
+  </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="334">
   <si>
     <t>S.No</t>
   </si>
@@ -1197,13 +1200,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1910,7 +1915,7 @@
       </c>
       <c r="N3" s="8" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,3),"P","A","L")</f>
-        <v>A</v>
+        <v>L</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
@@ -7146,7 +7151,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Select Form the DropDown" error="Select Form the DropDown" sqref="M2:AI81" xr:uid="{3B9CC5D6-AEB5-4F22-AC8C-FF10F3850228}">
       <formula1>"P,A,L"</formula1>
     </dataValidation>
@@ -7244,10 +7249,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.1796875" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="20.1796875" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
+    <col min="5" max="5" width="23.36328125" customWidth="1"/>
+    <col min="6" max="6" width="16.54296875" customWidth="1"/>
+    <col min="7" max="7" width="22.7265625" customWidth="1"/>
+    <col min="8" max="8" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.6328125" customWidth="1"/>
     <col min="10" max="10" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.36328125" bestFit="1" customWidth="1"/>
@@ -7256,84 +7261,114 @@
   </cols>
   <sheetData>
     <row r="2" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-    </row>
-    <row r="5" spans="4:13" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="D5" s="5" t="s">
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+    </row>
+    <row r="5" spans="4:13" s="20" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="20"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-    </row>
-    <row r="6" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" spans="4:13" s="20" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D6" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E6" s="8" t="str">
+        <f>VLOOKUP($D$6,RawData!$C$2:$H$82,2,FALSE)</f>
+        <v>R. VIGNESH</v>
+      </c>
+      <c r="F6" s="8" t="str">
+        <f>VLOOKUP($D$6,RawData!$C$2:$H$82,3,FALSE)</f>
+        <v>ITES</v>
+      </c>
+      <c r="G6" s="8">
+        <f>VLOOKUP($D$6,RawData!$C$2:$H$82,4,FALSE)</f>
+        <v>4360003876</v>
+      </c>
+      <c r="H6" s="8" t="str">
+        <f>VLOOKUP($D$6,RawData!$C$2:$H$82,5,FALSE)</f>
+        <v>rvignesh.itesites@gmail.com</v>
+      </c>
+      <c r="I6" s="8" t="str">
+        <f>VLOOKUP($D$6,RawData!$C$2:$H$82,6,FALSE)</f>
+        <v>Male</v>
+      </c>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.35">
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AC8A7F05-196B-4020-BB7F-28A723E14AA1}">
+          <x14:formula1>
+            <xm:f>RawData!$C$2:$C$82</xm:f>
+          </x14:formula1>
+          <xm:sqref>D6</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/Excel/LookupFunctions1.xlsx
+++ b/Excel/LookupFunctions1.xlsx
@@ -8,13 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E569756-895D-49A0-BC3A-000608E84A59}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184FF18E-6443-4CF5-B156-E9A564D51C53}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="1" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="3" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
     <sheet name="Vlookup" sheetId="2" r:id="rId2"/>
+    <sheet name="VData" sheetId="4" r:id="rId3"/>
+    <sheet name="VResult" sheetId="5" r:id="rId4"/>
+    <sheet name="HData" sheetId="6" r:id="rId5"/>
+    <sheet name="HResult" sheetId="7" r:id="rId6"/>
+    <sheet name="Liminations" sheetId="8" r:id="rId7"/>
+    <sheet name="IndexAndMatch" sheetId="9" r:id="rId8"/>
+    <sheet name="XLookup" sheetId="10" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RawData!$A$1:$AI$85</definedName>
@@ -29,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="391">
   <si>
     <t>S.No</t>
   </si>
@@ -1031,13 +1038,184 @@
   </si>
   <si>
     <t>Late</t>
+  </si>
+  <si>
+    <t>Student Code</t>
+  </si>
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>AF05174237</t>
+  </si>
+  <si>
+    <t>Machapatri G Sai Chiru</t>
+  </si>
+  <si>
+    <t>AF05199372</t>
+  </si>
+  <si>
+    <t>Shaikh Juned</t>
+  </si>
+  <si>
+    <t>AF05202233</t>
+  </si>
+  <si>
+    <t>Chavva manikanta</t>
+  </si>
+  <si>
+    <t>AF05202244</t>
+  </si>
+  <si>
+    <t>Nangunoori Tanmai</t>
+  </si>
+  <si>
+    <t>AF05202247</t>
+  </si>
+  <si>
+    <t>T Srivatshav</t>
+  </si>
+  <si>
+    <t>AF05202426</t>
+  </si>
+  <si>
+    <t>T Keerthan kumar</t>
+  </si>
+  <si>
+    <t>AF05202427</t>
+  </si>
+  <si>
+    <t>Kuruva Poojitha</t>
+  </si>
+  <si>
+    <t>AF05202436</t>
+  </si>
+  <si>
+    <t>Vemula Nehru Nithish</t>
+  </si>
+  <si>
+    <t>AF05202478</t>
+  </si>
+  <si>
+    <t>Priyanka Badiger</t>
+  </si>
+  <si>
+    <t>AF05202482</t>
+  </si>
+  <si>
+    <t>Bandi Niharika varma</t>
+  </si>
+  <si>
+    <t>AF05202485</t>
+  </si>
+  <si>
+    <t>Gorpadi parimala</t>
+  </si>
+  <si>
+    <t>AF05202513</t>
+  </si>
+  <si>
+    <t>Maroju Shiva kumar</t>
+  </si>
+  <si>
+    <t>AF05202522</t>
+  </si>
+  <si>
+    <t>Kancharl A ashwini</t>
+  </si>
+  <si>
+    <t>AF05202523</t>
+  </si>
+  <si>
+    <t>Onteddu krupakar</t>
+  </si>
+  <si>
+    <t>AF05202430</t>
+  </si>
+  <si>
+    <t>Mohammed Abrar Abbas</t>
+  </si>
+  <si>
+    <t>AF05202433</t>
+  </si>
+  <si>
+    <t>C Ravali</t>
+  </si>
+  <si>
+    <t>AF05202631</t>
+  </si>
+  <si>
+    <t>Ravi Revathi</t>
+  </si>
+  <si>
+    <t>AF05202632</t>
+  </si>
+  <si>
+    <t>Amruta I Zirli</t>
+  </si>
+  <si>
+    <t>AF05203213</t>
+  </si>
+  <si>
+    <t>N Manideepthi</t>
+  </si>
+  <si>
+    <t>AF05203209</t>
+  </si>
+  <si>
+    <t>Mekala Chintu</t>
+  </si>
+  <si>
+    <t>AF05203236</t>
+  </si>
+  <si>
+    <t>MACHAPATRI SRIJAN</t>
+  </si>
+  <si>
+    <t>AF05203244</t>
+  </si>
+  <si>
+    <t>SYED ZAMEERUDDIN</t>
+  </si>
+  <si>
+    <t>AF05204426</t>
+  </si>
+  <si>
+    <t>Garipelly Harshini</t>
+  </si>
+  <si>
+    <t>AF05207045</t>
+  </si>
+  <si>
+    <t>Jalli Rohith</t>
+  </si>
+  <si>
+    <t>AF05208247</t>
+  </si>
+  <si>
+    <t>Gangula Mallesh</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>Index MultiColumn</t>
+  </si>
+  <si>
+    <t>Index Single Column</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Index And Match</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1091,8 +1269,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1123,8 +1314,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1147,12 +1350,107 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1211,6 +1509,43 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7371,4 +7706,5068 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{289FED6F-ACD0-4468-9224-BEC5D4DBCF04}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" s="8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="8">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C4" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" s="8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="C6" s="8">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" s="8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="C10" s="8">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12" s="8">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C13" s="8">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="C14" s="8">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="C15" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="C16" s="8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="C18" s="8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C19" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C21" s="8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="C22" s="8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C23" s="8">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="C24" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="C25" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C26" s="8">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F880AB-D13C-4CD2-94A2-1A0643CB7050}">
+  <dimension ref="E5:G7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="21.36328125" customWidth="1"/>
+    <col min="6" max="6" width="27.453125" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:7" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="5:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E6" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="F6" s="28" t="str">
+        <f>UPPER(VLOOKUP(E6,VData!$A$2:$C$26,2,FALSE))</f>
+        <v>KANCHARL A ASHWINI</v>
+      </c>
+      <c r="G6" s="8">
+        <f>VLOOKUP(E6,VData!$A$2:$C$26,3,FALSE)</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="F7" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28309287-5748-4475-AD32-79E6241BFE4B}">
+  <dimension ref="B2:CD7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="31.54296875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="40.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="33.6328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="31" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.08984375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="30" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="42.453125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="40.453125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="33.6328125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="27" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="38" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="34.26953125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="26" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="31.6328125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="29" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="33.90625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="26.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:82" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="AP2" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="AQ2" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="AR2" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="AS2" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="AT2" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="AU2" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="AV2" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="AW2" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="AX2" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AY2" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="AZ2" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="BA2" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="BB2" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="BC2" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="BD2" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="BE2" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="BF2" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="BG2" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="BH2" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="BI2" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="BJ2" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="BK2" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="BL2" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="BM2" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="BN2" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="BO2" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="BP2" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="BQ2" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="BR2" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="BS2" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="BT2" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="BU2" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="BV2" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="BW2" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="BX2" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="BY2" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="BZ2" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="CA2" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="CB2" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="CC2" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="CD2" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="2:82" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="O3" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="P3" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q3" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="T3" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="U3" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="V3" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="W3" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="X3" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y3" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z3" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB3" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC3" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD3" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE3" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF3" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG3" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH3" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI3" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="AJ3" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="AK3" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="AL3" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM3" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AN3" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="AO3" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="AP3" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="AQ3" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="AR3" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="AS3" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="AT3" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="AU3" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="AV3" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="AW3" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="AX3" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="AY3" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="AZ3" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="BA3" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="BB3" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="BC3" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="BD3" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="BE3" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="BF3" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="BG3" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="BH3" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="BI3" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="BJ3" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="BK3" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="BL3" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="BM3" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="BN3" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="BO3" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="BP3" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="BQ3" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="BR3" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="BS3" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="BT3" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="BU3" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="BV3" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="BW3" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="BX3" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="BY3" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="BZ3" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="CA3" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="CB3" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="CC3" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="CD3" s="32" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:82" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B4" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="T4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="W4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="X4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BA4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BC4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="BH4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BI4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BJ4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BL4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BM4" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BO4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="BP4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BQ4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BR4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BS4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="BT4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BU4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BV4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BX4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="CA4" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="CB4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="CC4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="CD4" s="32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:82" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7">
+        <v>6399221384</v>
+      </c>
+      <c r="D5" s="7">
+        <v>8732960724</v>
+      </c>
+      <c r="E5" s="7">
+        <v>3928683138</v>
+      </c>
+      <c r="F5" s="7">
+        <v>6302977515</v>
+      </c>
+      <c r="G5" s="7">
+        <v>3285643454</v>
+      </c>
+      <c r="H5" s="7">
+        <v>6204804746</v>
+      </c>
+      <c r="I5" s="7">
+        <v>8402592334</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1770577932</v>
+      </c>
+      <c r="K5" s="7">
+        <v>1087593685</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1693682470</v>
+      </c>
+      <c r="M5" s="7">
+        <v>1821308586</v>
+      </c>
+      <c r="N5" s="7">
+        <v>1683546545</v>
+      </c>
+      <c r="O5" s="7">
+        <v>5506439807</v>
+      </c>
+      <c r="P5" s="7">
+        <v>3565997600</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>2685014153</v>
+      </c>
+      <c r="R5" s="7">
+        <v>8144007188</v>
+      </c>
+      <c r="S5" s="7">
+        <v>5451418853</v>
+      </c>
+      <c r="T5" s="7">
+        <v>2352093828</v>
+      </c>
+      <c r="U5" s="7">
+        <v>4851546652</v>
+      </c>
+      <c r="V5" s="7">
+        <v>6604423032</v>
+      </c>
+      <c r="W5" s="7">
+        <v>4267924443</v>
+      </c>
+      <c r="X5" s="7">
+        <v>2776428499</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>2344591250</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>4564000793</v>
+      </c>
+      <c r="AA5" s="7">
+        <v>7831800139</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>1359937879</v>
+      </c>
+      <c r="AC5" s="7">
+        <v>8357059907</v>
+      </c>
+      <c r="AD5" s="7">
+        <v>8195300576</v>
+      </c>
+      <c r="AE5" s="7">
+        <v>3908490120</v>
+      </c>
+      <c r="AF5" s="7">
+        <v>6654686097</v>
+      </c>
+      <c r="AG5" s="7">
+        <v>3176554504</v>
+      </c>
+      <c r="AH5" s="7">
+        <v>7375541777</v>
+      </c>
+      <c r="AI5" s="7">
+        <v>2307603936</v>
+      </c>
+      <c r="AJ5" s="7">
+        <v>7539961295</v>
+      </c>
+      <c r="AK5" s="7">
+        <v>8714929594</v>
+      </c>
+      <c r="AL5" s="7">
+        <v>6748495954</v>
+      </c>
+      <c r="AM5" s="7">
+        <v>5598318903</v>
+      </c>
+      <c r="AN5" s="7">
+        <v>5366755536</v>
+      </c>
+      <c r="AO5" s="7">
+        <v>5685425899</v>
+      </c>
+      <c r="AP5" s="7">
+        <v>8546891943</v>
+      </c>
+      <c r="AQ5" s="7">
+        <v>7905481507</v>
+      </c>
+      <c r="AR5" s="7">
+        <v>5681445328</v>
+      </c>
+      <c r="AS5" s="7">
+        <v>1576469041</v>
+      </c>
+      <c r="AT5" s="7">
+        <v>7244391357</v>
+      </c>
+      <c r="AU5" s="7">
+        <v>5713887644</v>
+      </c>
+      <c r="AV5" s="7">
+        <v>4360003876</v>
+      </c>
+      <c r="AW5" s="7">
+        <v>6232183694</v>
+      </c>
+      <c r="AX5" s="7">
+        <v>6682877186</v>
+      </c>
+      <c r="AY5" s="7">
+        <v>8911831176</v>
+      </c>
+      <c r="AZ5" s="7">
+        <v>5328455783</v>
+      </c>
+      <c r="BA5" s="7">
+        <v>4825148027</v>
+      </c>
+      <c r="BB5" s="7">
+        <v>3228331930</v>
+      </c>
+      <c r="BC5" s="7">
+        <v>7158666834</v>
+      </c>
+      <c r="BD5" s="7">
+        <v>7998839021</v>
+      </c>
+      <c r="BE5" s="7">
+        <v>8550635195</v>
+      </c>
+      <c r="BF5" s="7">
+        <v>8733465367</v>
+      </c>
+      <c r="BG5" s="7">
+        <v>6153044829</v>
+      </c>
+      <c r="BH5" s="7">
+        <v>4496254693</v>
+      </c>
+      <c r="BI5" s="7">
+        <v>2881088394</v>
+      </c>
+      <c r="BJ5" s="7">
+        <v>3401449282</v>
+      </c>
+      <c r="BK5" s="7">
+        <v>4405995363</v>
+      </c>
+      <c r="BL5" s="7">
+        <v>2219599156</v>
+      </c>
+      <c r="BM5" s="7">
+        <v>3482112190</v>
+      </c>
+      <c r="BN5" s="7">
+        <v>8411360361</v>
+      </c>
+      <c r="BO5" s="7">
+        <v>2842414479</v>
+      </c>
+      <c r="BP5" s="7">
+        <v>5876113945</v>
+      </c>
+      <c r="BQ5" s="7">
+        <v>4273126076</v>
+      </c>
+      <c r="BR5" s="7">
+        <v>8077085042</v>
+      </c>
+      <c r="BS5" s="7">
+        <v>8112643867</v>
+      </c>
+      <c r="BT5" s="7">
+        <v>3685782386</v>
+      </c>
+      <c r="BU5" s="7">
+        <v>6205596324</v>
+      </c>
+      <c r="BV5" s="7">
+        <v>6578497608</v>
+      </c>
+      <c r="BW5" s="7">
+        <v>2602080020</v>
+      </c>
+      <c r="BX5" s="7">
+        <v>8796416295</v>
+      </c>
+      <c r="BY5" s="7">
+        <v>5978571640</v>
+      </c>
+      <c r="BZ5" s="7">
+        <v>5716170881</v>
+      </c>
+      <c r="CA5" s="7">
+        <v>6927479136</v>
+      </c>
+      <c r="CB5" s="7">
+        <v>8625176197</v>
+      </c>
+      <c r="CC5" s="7">
+        <v>3221738150</v>
+      </c>
+      <c r="CD5" s="7">
+        <v>2217423855</v>
+      </c>
+    </row>
+    <row r="6" spans="2:82" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="U6" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="V6" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="X6" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y6" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z6" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA6" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB6" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC6" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD6" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE6" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF6" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG6" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH6" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI6" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ6" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK6" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL6" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="AM6" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="AN6" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AO6" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP6" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="AQ6" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="AR6" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="AS6" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="AT6" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="AU6" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="AV6" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="AW6" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="AX6" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="AY6" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="AZ6" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="BA6" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="BB6" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="BC6" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD6" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="BE6" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="BF6" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="BG6" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="BH6" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="BI6" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="BJ6" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="BK6" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="BL6" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="BM6" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="BN6" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="BO6" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="BP6" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="BQ6" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="BR6" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="BS6" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="BT6" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="BU6" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="BV6" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="BW6" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="BX6" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="BY6" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="BZ6" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="CA6" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="CB6" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="CC6" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="CD6" s="34" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" spans="2:82" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="P7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="T7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="U7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="V7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="W7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="X7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AQ7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AR7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AT7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AU7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AV7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AX7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BB7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BC7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BD7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BE7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="BF7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="BG7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BH7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BI7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="BJ7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BK7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BL7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BM7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BN7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="BO7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BP7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="BQ7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BR7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="BS7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BT7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="BU7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BV7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BW7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BX7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BY7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="BZ7" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="CA7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="CB7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="CC7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="CD7" s="32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E6" r:id="rId1" xr:uid="{CC88AA6E-FF13-456D-B10A-F48C6AF3B137}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{6A7931CF-1226-49FB-B5FB-C178261A131F}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{9B42CCFD-A069-4D00-BEE3-DEE00293FB82}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{2DA282C9-3DCF-41F9-B776-BAD0991D5E17}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{CD5EC76F-E548-42F4-B848-1F408981AE48}"/>
+    <hyperlink ref="H6" r:id="rId6" xr:uid="{0545ABD1-6817-4680-8439-2F7C1B40FE4D}"/>
+    <hyperlink ref="I6" r:id="rId7" xr:uid="{57EDB623-2F12-4673-B81C-A380BC0A0B00}"/>
+    <hyperlink ref="J6" r:id="rId8" xr:uid="{6EF59730-8062-4167-8F41-DD9D86FCC09F}"/>
+    <hyperlink ref="K6" r:id="rId9" xr:uid="{A6B3B2F1-30FB-4A96-8FB7-AACCD6908017}"/>
+    <hyperlink ref="L6" r:id="rId10" xr:uid="{4872FBAD-40F3-41ED-A88B-2A9E6EEF530F}"/>
+    <hyperlink ref="M6" r:id="rId11" xr:uid="{E31D2622-311C-49F6-988F-B8FE269B3AD1}"/>
+    <hyperlink ref="N6" r:id="rId12" xr:uid="{2163D210-3B1D-4ABD-80A7-B3084CEDD7F1}"/>
+    <hyperlink ref="O6" r:id="rId13" xr:uid="{277678ED-20ED-4F4F-BEE3-2A2F809DDB30}"/>
+    <hyperlink ref="P6" r:id="rId14" xr:uid="{211E279B-A463-4139-BF8E-134569291520}"/>
+    <hyperlink ref="Q6" r:id="rId15" xr:uid="{03C401CC-4C66-4604-B994-9C2B57AC49AC}"/>
+    <hyperlink ref="R6" r:id="rId16" xr:uid="{6E924AF3-162D-428E-BF27-441AFAE194AE}"/>
+    <hyperlink ref="S6" r:id="rId17" xr:uid="{C3C11AA5-FF2C-4C47-BC63-D278B00884DA}"/>
+    <hyperlink ref="T6" r:id="rId18" xr:uid="{19E6D62D-D4C4-4138-9E98-FF577DA786C9}"/>
+    <hyperlink ref="U6" r:id="rId19" xr:uid="{1292C1B8-11B6-474A-80DD-692351EF6B53}"/>
+    <hyperlink ref="V6" r:id="rId20" xr:uid="{1249B6F3-8654-4FE1-8D8B-B48EA49DA876}"/>
+    <hyperlink ref="W6" r:id="rId21" xr:uid="{9286337C-7017-468F-A7C2-322FF5C46C5E}"/>
+    <hyperlink ref="X6" r:id="rId22" xr:uid="{AA26A96B-8144-4026-98B1-9EC2AE6383AB}"/>
+    <hyperlink ref="Y6" r:id="rId23" xr:uid="{EA63605F-A09A-42F4-9DDF-62413941D3E5}"/>
+    <hyperlink ref="Z6" r:id="rId24" xr:uid="{CB1619E7-BA79-44BE-9576-9362E03E021A}"/>
+    <hyperlink ref="AA6" r:id="rId25" xr:uid="{48DE3BE2-65D0-451D-A511-272F44C236A7}"/>
+    <hyperlink ref="AB6" r:id="rId26" xr:uid="{16CD9C69-5227-4BC2-8DEC-42CD7F37A860}"/>
+    <hyperlink ref="AC6" r:id="rId27" xr:uid="{F7014700-3512-44EF-9D4B-DE14F9159D93}"/>
+    <hyperlink ref="AD6" r:id="rId28" xr:uid="{FE68F909-E897-4D01-8753-4EE39C0AF77A}"/>
+    <hyperlink ref="AE6" r:id="rId29" xr:uid="{0F582A67-0D25-4901-824F-5449FC73D503}"/>
+    <hyperlink ref="AF6" r:id="rId30" xr:uid="{E3EE5711-B1EF-4672-A39A-3779C88D5EDA}"/>
+    <hyperlink ref="AG6" r:id="rId31" xr:uid="{174767EE-9FAD-4B3A-A185-252E6CD37093}"/>
+    <hyperlink ref="AH6" r:id="rId32" xr:uid="{CE34D7DE-4ADF-4E7C-8F6F-28AF84D87986}"/>
+    <hyperlink ref="AI6" r:id="rId33" xr:uid="{06BD0C4E-458D-4320-8101-0FB255B50414}"/>
+    <hyperlink ref="AJ6" r:id="rId34" xr:uid="{98C3BBA8-FB43-4050-A176-AFF9F99F3EAC}"/>
+    <hyperlink ref="AK6" r:id="rId35" xr:uid="{EDC37373-9F86-4B59-BFB3-B5615C1D063F}"/>
+    <hyperlink ref="AL6" r:id="rId36" xr:uid="{F281C649-156B-474F-9664-C04FC55B37EF}"/>
+    <hyperlink ref="AM6" r:id="rId37" xr:uid="{5A57A1E9-EC11-46AD-861F-14411962F2FF}"/>
+    <hyperlink ref="AN6" r:id="rId38" xr:uid="{D25C4643-00B9-4934-B518-22043725FDEF}"/>
+    <hyperlink ref="AO6" r:id="rId39" xr:uid="{6545B1ED-38BC-4B22-BE90-0C4D8BF3AD62}"/>
+    <hyperlink ref="AP6" r:id="rId40" xr:uid="{A9CD5E89-FD73-47D6-AB18-4BA35EA4EFD3}"/>
+    <hyperlink ref="AQ6" r:id="rId41" xr:uid="{76B50A8E-802E-4341-8968-321A22AB58CA}"/>
+    <hyperlink ref="AR6" r:id="rId42" xr:uid="{731347FF-95C3-476C-9E9D-04D47DEB7C59}"/>
+    <hyperlink ref="AS6" r:id="rId43" xr:uid="{2138744B-623E-45A2-87F7-65C89040AE09}"/>
+    <hyperlink ref="AT6" r:id="rId44" xr:uid="{7AF6613E-2912-46F3-8EC6-C09213B1145E}"/>
+    <hyperlink ref="AU6" r:id="rId45" xr:uid="{440B21B8-34B9-407E-97BA-260D20C9B64D}"/>
+    <hyperlink ref="AV6" r:id="rId46" xr:uid="{CA696B43-5DDD-4163-9364-1956DCD5863A}"/>
+    <hyperlink ref="AW6" r:id="rId47" xr:uid="{2B5117F5-ACDF-4E5D-BBF1-7307575C59DB}"/>
+    <hyperlink ref="AX6" r:id="rId48" xr:uid="{363489E9-2634-4B73-8947-85B26DE0F300}"/>
+    <hyperlink ref="AY6" r:id="rId49" xr:uid="{A74B6298-0903-4309-A045-AD8E836B7E4C}"/>
+    <hyperlink ref="AZ6" r:id="rId50" xr:uid="{774D8D01-17FB-49FC-89D3-863AB172F48A}"/>
+    <hyperlink ref="BA6" r:id="rId51" xr:uid="{B27082FF-47D0-482E-81D5-B645F897E0D3}"/>
+    <hyperlink ref="BB6" r:id="rId52" xr:uid="{F0559A9E-B656-422A-BF5A-D76EE24F89C2}"/>
+    <hyperlink ref="BC6" r:id="rId53" xr:uid="{634F0517-326B-40AE-AA7D-C0669F988008}"/>
+    <hyperlink ref="BD6" r:id="rId54" xr:uid="{0EE2B995-7765-4584-8398-B6934E9ED48E}"/>
+    <hyperlink ref="BE6" r:id="rId55" xr:uid="{7191123D-805F-4364-8734-492B7F07826C}"/>
+    <hyperlink ref="BF6" r:id="rId56" xr:uid="{FDAA3A87-55B4-4154-9B14-0E3C7DC9FC2E}"/>
+    <hyperlink ref="BG6" r:id="rId57" xr:uid="{08B71721-B10F-441C-9751-3977AE583D6B}"/>
+    <hyperlink ref="BH6" r:id="rId58" xr:uid="{5B82C568-ADF9-478E-90C2-88F5D58259D9}"/>
+    <hyperlink ref="BI6" r:id="rId59" xr:uid="{7E30535F-E14D-45A8-8DF3-CCA4F4074827}"/>
+    <hyperlink ref="BJ6" r:id="rId60" xr:uid="{9DB93D84-F23E-4A46-912B-030E092646E2}"/>
+    <hyperlink ref="BK6" r:id="rId61" xr:uid="{859A8EE5-762B-4E03-94CE-1ED1FC2161CE}"/>
+    <hyperlink ref="BL6" r:id="rId62" xr:uid="{62112E41-4C5D-4628-8E46-5C7CBAA8D749}"/>
+    <hyperlink ref="BM6" r:id="rId63" xr:uid="{7A4AB763-C99D-4DE7-82A2-9EA3659BCFB8}"/>
+    <hyperlink ref="BN6" r:id="rId64" xr:uid="{3FAD7BCB-C5B1-4E0A-9391-15C95813DFC5}"/>
+    <hyperlink ref="BO6" r:id="rId65" xr:uid="{F38662A9-D86B-4820-A80C-405553EEBB57}"/>
+    <hyperlink ref="BP6" r:id="rId66" xr:uid="{F4BCB1DB-C5F2-4069-932A-5F55EFD3B7A5}"/>
+    <hyperlink ref="BQ6" r:id="rId67" xr:uid="{A2B1A73D-C80D-4084-8D8B-5397B91C9040}"/>
+    <hyperlink ref="BR6" r:id="rId68" xr:uid="{35521D74-BA79-4D13-91E7-E7D7A6813EBA}"/>
+    <hyperlink ref="BS6" r:id="rId69" xr:uid="{D9A5FC2B-DD0E-4009-925C-AF2819F11068}"/>
+    <hyperlink ref="BT6" r:id="rId70" xr:uid="{80A17ACB-8D7D-4284-A39E-0E13DE04B211}"/>
+    <hyperlink ref="BU6" r:id="rId71" xr:uid="{9645C920-689A-4832-B8E4-D479015156CC}"/>
+    <hyperlink ref="BV6" r:id="rId72" xr:uid="{D7E6C3EC-CD44-4203-8058-C5FE69F72021}"/>
+    <hyperlink ref="BW6" r:id="rId73" xr:uid="{51ACADDF-00B5-4488-B20D-5E68DBC2313F}"/>
+    <hyperlink ref="BX6" r:id="rId74" xr:uid="{1ABB7549-5BF0-48E1-8592-6F148427EAA8}"/>
+    <hyperlink ref="BY6" r:id="rId75" xr:uid="{B77D62B5-208B-4EB1-B749-38F9575F2B3E}"/>
+    <hyperlink ref="BZ6" r:id="rId76" xr:uid="{C7AB6A2A-DD2B-4669-A313-C779F98DCB19}"/>
+    <hyperlink ref="CA6" r:id="rId77" xr:uid="{F76F2775-2483-4F0D-A0B3-6DA3B7BE83A6}"/>
+    <hyperlink ref="CB6" r:id="rId78" xr:uid="{D32E8228-2125-447A-8A72-ED5FD4172AC0}"/>
+    <hyperlink ref="CC6" r:id="rId79" xr:uid="{F07B6BCB-8652-4F2C-B13C-6FD902CEE934}"/>
+    <hyperlink ref="CD6" r:id="rId80" xr:uid="{FA521B4E-8FF8-452F-964A-89597B15E482}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDB9094-8273-4A0A-A89A-87F8A1046DB3}">
+  <dimension ref="F7:H8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.7265625" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="6:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="F7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="F8" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" s="8" t="str">
+        <f>HLOOKUP($F$8,HData!$C$2:$CD$7,2,FALSE)</f>
+        <v>R. VIGNESH</v>
+      </c>
+      <c r="H8" s="8" t="str">
+        <f>HLOOKUP($F$8,HData!$C$2:$CD$7,3,FALSE)</f>
+        <v>ITES</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1E9225D5-1E10-4A80-B306-0E14DF8187F5}">
+          <x14:formula1>
+            <xm:f>RawData!$C$2:$C$82</xm:f>
+          </x14:formula1>
+          <xm:sqref>F8</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C864E1D-F0E0-48D3-A141-473B8953EB5C}">
+  <dimension ref="B1:L81"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.90625" customWidth="1"/>
+    <col min="11" max="11" width="16.36328125" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8">
+        <v>6399221384</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="8">
+        <v>8732960724</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="8">
+        <v>3928683138</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="8">
+        <v>6302977515</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="8">
+        <v>3285643454</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8">
+        <v>6204804746</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="8">
+        <v>8402592334</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="7" t="str">
+        <f>VLOOKUP($I$8,$B$2:$G$81,2,FALSE)</f>
+        <v>B SANDEEP ROY</v>
+      </c>
+      <c r="K8" s="7" t="str">
+        <f>VLOOKUP($I$8,$B$2:$G$81,3,FALSE)</f>
+        <v>ITES</v>
+      </c>
+      <c r="L8" s="7">
+        <f>VLOOKUP($I$8,$B$2:$G$81,4,FALSE)</f>
+        <v>6204804746</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1770577932</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1087593685</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1693682470</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1821308586</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1683546545</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="8">
+        <v>5506439807</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="7" t="str">
+        <f>VLOOKUP($I$8,$B$2:$G$81,3,FALSE)</f>
+        <v>ITES</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B15" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3565997600</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2685014153</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="8">
+        <v>8144007188</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="8">
+        <v>5451418853</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2352093828</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4851546652</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="8">
+        <v>6604423032</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="8">
+        <v>4267924443</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2776428499</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2344591250</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="8">
+        <v>4564000793</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="8">
+        <v>7831800139</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B27" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1359937879</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="8">
+        <v>8357059907</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="8">
+        <v>8195300576</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3908490120</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="8">
+        <v>6654686097</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="8">
+        <v>3176554504</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B33" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="8">
+        <v>7375541777</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B34" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="8">
+        <v>2307603936</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="8">
+        <v>7539961295</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="8">
+        <v>8714929594</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B37" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="8">
+        <v>6748495954</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="8">
+        <v>5598318903</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="8">
+        <v>5366755536</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="8">
+        <v>5685425899</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="8">
+        <v>8546891943</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="8">
+        <v>7905481507</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B43" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="8">
+        <v>5681445328</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1576469041</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="8">
+        <v>7244391357</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B46" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="8">
+        <v>5713887644</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B47" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="8">
+        <v>4360003876</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B48" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="8">
+        <v>6232183694</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B49" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="8">
+        <v>6682877186</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B50" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="8">
+        <v>8911831176</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B51" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="8">
+        <v>5328455783</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B52" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="8">
+        <v>4825148027</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B53" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="8">
+        <v>3228331930</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B54" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="8">
+        <v>7158666834</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B55" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="8">
+        <v>7998839021</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B56" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="8">
+        <v>8550635195</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B57" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="8">
+        <v>8733465367</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B58" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="8">
+        <v>6153044829</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B59" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="8">
+        <v>4496254693</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B60" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="8">
+        <v>2881088394</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B61" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="8">
+        <v>3401449282</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B62" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="8">
+        <v>4405995363</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B63" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="8">
+        <v>2219599156</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B64" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="8">
+        <v>3482112190</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B65" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="8">
+        <v>8411360361</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B66" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2842414479</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="G66" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B67" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="8">
+        <v>5876113945</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B68" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="8">
+        <v>4273126076</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B69" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="8">
+        <v>8077085042</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B70" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" s="8">
+        <v>8112643867</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B71" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="8">
+        <v>3685782386</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B72" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="8">
+        <v>6205596324</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B73" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="8">
+        <v>6578497608</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B74" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="8">
+        <v>2602080020</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B75" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="8">
+        <v>8796416295</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B76" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" s="8">
+        <v>5978571640</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B77" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="8">
+        <v>5716170881</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B78" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="8">
+        <v>6927479136</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B79" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="8">
+        <v>8625176197</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B80" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="8">
+        <v>3221738150</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B81" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81" s="8">
+        <v>2217423855</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{6943E37F-BE0E-4591-A6F6-7D28447CB517}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{DDD4A9F0-DA53-4FB5-AF62-0C2444BE95C7}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{7EC446AE-AC49-4409-B4A0-FB28D014BBC4}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{D3226654-88B7-4F6F-B176-0E480EA0D834}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{1AD5482B-AC4B-41ED-8356-6AD9814D21DA}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{84D5582D-B820-4D5C-88FA-B35B77A940D4}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{39BCA94F-9C04-4388-AD25-CDFEA938E7AF}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{1AC0DA67-77A1-43A9-9103-03CCB7F32691}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{F7110F2C-5A64-41D1-B7B3-281DE8C6D51C}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{B44F1FC4-1E31-4F8A-8670-114EAE6EA6BC}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{14D19F92-B046-469F-A877-4B1300E6D689}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{147A47B7-F155-4336-9788-6B179D5BF187}"/>
+    <hyperlink ref="F14" r:id="rId13" xr:uid="{6AA18A9D-C782-4534-9C57-135D44AFFEE5}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{59EEDF3C-6696-46C2-AA64-F4DA51473AFB}"/>
+    <hyperlink ref="F16" r:id="rId15" xr:uid="{053C18E4-09B4-47F9-BF70-657337BC4663}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{731ABF34-9EC4-4A95-AC5C-B50636C71CF0}"/>
+    <hyperlink ref="F18" r:id="rId17" xr:uid="{7148438B-3343-40D4-AA50-DCF01AACEA03}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{88AA0A7E-A7AB-44D7-8920-EF90BB22AAE2}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{FEE72464-922B-49C9-8F4E-5CE06C964B8C}"/>
+    <hyperlink ref="F21" r:id="rId20" xr:uid="{E16A2264-A890-4E46-AA74-CEE52774FA23}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{46682D2B-31DF-47D8-89EF-3E5A45E6D74F}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{D182E977-89F5-4E26-BF96-0A6D1AF86C4E}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{D87E773D-65CD-4014-ABF9-DE00AA0B4CFC}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{7FC92933-4D91-432A-8F01-E4BF9EED3C23}"/>
+    <hyperlink ref="F26" r:id="rId25" xr:uid="{7BD8642C-1553-49EA-9A61-A591879DFD13}"/>
+    <hyperlink ref="F27" r:id="rId26" xr:uid="{D6718DB4-B245-4640-B742-C10798DCCE30}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{AEE2EBF9-0B62-47CE-BCA3-AEBE809AFC13}"/>
+    <hyperlink ref="F29" r:id="rId28" xr:uid="{3C7DEE42-AF07-471F-9704-0507636B5697}"/>
+    <hyperlink ref="F30" r:id="rId29" xr:uid="{577DA0CE-89F1-4842-B2BE-63F6D03BAF32}"/>
+    <hyperlink ref="F31" r:id="rId30" xr:uid="{229F3285-99D1-433B-B9CB-C280A1D40D0E}"/>
+    <hyperlink ref="F32" r:id="rId31" xr:uid="{4466B59F-44A6-48A9-AFE1-82D34906FB66}"/>
+    <hyperlink ref="F33" r:id="rId32" xr:uid="{1014172D-ED88-4CDC-A21A-CDB7B92A8BE2}"/>
+    <hyperlink ref="F34" r:id="rId33" xr:uid="{8B63EDD7-6016-4E6F-86D7-F95B28BCA162}"/>
+    <hyperlink ref="F35" r:id="rId34" xr:uid="{18DB288E-09D4-4807-BE1C-058C18A1FA4E}"/>
+    <hyperlink ref="F36" r:id="rId35" xr:uid="{6F82EF6D-B99C-4307-9911-4521CEB064AC}"/>
+    <hyperlink ref="F37" r:id="rId36" xr:uid="{7FFAE770-A5CC-4C79-8151-8C13F9AE806D}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{184C7823-10F9-4327-AE43-6B21495D0EF1}"/>
+    <hyperlink ref="F39" r:id="rId38" xr:uid="{58C0AF87-4056-4128-9785-9B4EFC364CF7}"/>
+    <hyperlink ref="F40" r:id="rId39" xr:uid="{FE6AC069-D8B7-4F50-81EB-14F4250AB5BB}"/>
+    <hyperlink ref="F41" r:id="rId40" xr:uid="{265F0D60-9987-4E1F-A126-AFF5099FAD95}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{5560D5AE-C718-48AF-A6BF-D2385BEEFF8B}"/>
+    <hyperlink ref="F43" r:id="rId42" xr:uid="{884AE74E-97A2-45F3-B739-C302EAE3CB81}"/>
+    <hyperlink ref="F44" r:id="rId43" xr:uid="{47E531DE-C8B3-4339-A582-8E4759D443FA}"/>
+    <hyperlink ref="F45" r:id="rId44" xr:uid="{5E67178E-989E-4326-A3FB-2A5CE07839C3}"/>
+    <hyperlink ref="F46" r:id="rId45" xr:uid="{E6E99883-FABB-4209-B24F-9C0F61AA4D4E}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{992C83D4-6B57-4C6B-A38E-6915C5EC8699}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{1A2CD049-9613-42B0-9D9F-0666E1B48968}"/>
+    <hyperlink ref="F49" r:id="rId48" xr:uid="{A31C9221-A794-4C62-BA3B-E8E2075F52AE}"/>
+    <hyperlink ref="F50" r:id="rId49" xr:uid="{61064FB7-9B52-46DC-9947-5F401B6E4816}"/>
+    <hyperlink ref="F51" r:id="rId50" xr:uid="{877A8C5F-0E67-4CD2-A82F-DB2D51675824}"/>
+    <hyperlink ref="F52" r:id="rId51" xr:uid="{074351BD-7E48-4D7E-AF0F-08B61C07A958}"/>
+    <hyperlink ref="F53" r:id="rId52" xr:uid="{010F8ACA-77ED-4660-A700-77AEA480C818}"/>
+    <hyperlink ref="F54" r:id="rId53" xr:uid="{F9489530-D1FD-4073-85AE-A8A303E66D9E}"/>
+    <hyperlink ref="F55" r:id="rId54" xr:uid="{4E0A27AC-60C2-474F-9F11-62AF70A6BE86}"/>
+    <hyperlink ref="F56" r:id="rId55" xr:uid="{22B81662-CCB4-4EE4-B6FD-1C4A05007CB5}"/>
+    <hyperlink ref="F57" r:id="rId56" xr:uid="{8BD23F6D-FBDD-4771-92F1-E6C199B3C46B}"/>
+    <hyperlink ref="F58" r:id="rId57" xr:uid="{92A3361C-42D0-4EA7-808B-02BABE32A965}"/>
+    <hyperlink ref="F59" r:id="rId58" xr:uid="{5FACC9F7-35C3-4BF5-AD4F-164F1FE7E726}"/>
+    <hyperlink ref="F60" r:id="rId59" xr:uid="{B441F379-6B9E-479F-A523-D5BC8EB63C4D}"/>
+    <hyperlink ref="F61" r:id="rId60" xr:uid="{CFE2FD04-F224-4D13-801A-76E90ADAB18F}"/>
+    <hyperlink ref="F62" r:id="rId61" xr:uid="{920CB2CD-FDBD-450C-8376-E089DFF7EA3C}"/>
+    <hyperlink ref="F63" r:id="rId62" xr:uid="{0CE60922-9603-4A9D-BEF8-93C5193C95B9}"/>
+    <hyperlink ref="F64" r:id="rId63" xr:uid="{BF623135-CAD7-44D2-B5F1-4C74A9BA41BE}"/>
+    <hyperlink ref="F65" r:id="rId64" xr:uid="{BBEAAC60-5C9A-4642-848E-9FFF49BEE65D}"/>
+    <hyperlink ref="F66" r:id="rId65" xr:uid="{CC9B4ED2-5106-4A93-977B-2D3006201848}"/>
+    <hyperlink ref="F67" r:id="rId66" xr:uid="{25110AE2-39C6-4612-92F5-3599D3BC96E1}"/>
+    <hyperlink ref="F68" r:id="rId67" xr:uid="{54D2D0F8-59CC-4A34-A105-FFDD89FDCC1D}"/>
+    <hyperlink ref="F69" r:id="rId68" xr:uid="{1D64158C-8A4C-4C96-B1E1-3930C60F7404}"/>
+    <hyperlink ref="F70" r:id="rId69" xr:uid="{04F6593B-321C-4EF9-99F2-02E6CB3B6967}"/>
+    <hyperlink ref="F71" r:id="rId70" xr:uid="{01A02736-F06E-4CAE-BF70-477F1A62C58A}"/>
+    <hyperlink ref="F72" r:id="rId71" xr:uid="{4FC38C7E-D28B-49CA-93A6-E03338048D79}"/>
+    <hyperlink ref="F73" r:id="rId72" xr:uid="{EF1462A7-E3F3-499B-88CD-EC708B7C96EA}"/>
+    <hyperlink ref="F74" r:id="rId73" xr:uid="{BC5F0E95-03A9-41DA-BF05-D7C5A2647688}"/>
+    <hyperlink ref="F75" r:id="rId74" xr:uid="{D943752C-8978-4026-8820-4E840B78C676}"/>
+    <hyperlink ref="F76" r:id="rId75" xr:uid="{AF040A4F-8111-45F0-B849-F590460FF188}"/>
+    <hyperlink ref="F77" r:id="rId76" xr:uid="{32D4A9F8-F159-4F1B-A327-D61C0DC20347}"/>
+    <hyperlink ref="F78" r:id="rId77" xr:uid="{F77AF0B9-5612-4F04-89E2-6055CCF19D60}"/>
+    <hyperlink ref="F79" r:id="rId78" xr:uid="{01346624-D180-412A-892F-FE0139E6B735}"/>
+    <hyperlink ref="F80" r:id="rId79" xr:uid="{E7C5F277-8805-4F9B-8F2D-225682D76ABC}"/>
+    <hyperlink ref="F81" r:id="rId80" xr:uid="{2047F7F9-9CFF-44BB-B494-08C02829D0AB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCC2C67-833C-46AB-A423-5F580E3249B4}">
+  <dimension ref="A1:J85"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.90625" customWidth="1"/>
+    <col min="7" max="7" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="14.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="8">
+        <v>6399221384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="8">
+        <v>8732960724</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="8">
+        <v>3928683138</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="8">
+        <v>6302977515</v>
+      </c>
+      <c r="G5" s="7" t="str">
+        <f>INDEX($A$2:$D$81,10,2)</f>
+        <v>BURRI VINITHA</v>
+      </c>
+      <c r="H5" s="8" t="str">
+        <f>INDEX(B2:B1000,10)</f>
+        <v>BURRI VINITHA</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8">
+        <v>3285643454</v>
+      </c>
+      <c r="G6" s="8">
+        <f>INDEX($A$2:$D$81,10,4)</f>
+        <v>1693682470</v>
+      </c>
+      <c r="H6" s="8">
+        <f>INDEX($D$2:$D$81,10)</f>
+        <v>1693682470</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="8">
+        <v>6204804746</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="8">
+        <v>8402592334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1770577932</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1087593685</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1693682470</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1821308586</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="8">
+        <f>MATCH($F$12,$A$2:$A$82,0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1683546545</v>
+      </c>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="8">
+        <v>5506439807</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="8">
+        <v>3565997600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2685014153</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="8">
+        <v>8144007188</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="8">
+        <v>5451418853</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="26" t="str">
+        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),2)</f>
+        <v>K. SANTOSHI</v>
+      </c>
+      <c r="I18" s="8" t="str">
+        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),3)</f>
+        <v>Full Stack</v>
+      </c>
+      <c r="J18" s="8">
+        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),4)</f>
+        <v>1359937879</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="8">
+        <v>2352093828</v>
+      </c>
+      <c r="H19" s="36" t="str">
+        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),MATCH($H$17,$A$1:$D$1,0))</f>
+        <v>K. SANTOSHI</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="8">
+        <v>4851546652</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="8">
+        <v>6604423032</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="8">
+        <v>4267924443</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="8">
+        <v>2776428499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="8">
+        <v>2344591250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="8">
+        <v>4564000793</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="8">
+        <v>7831800139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1359937879</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="8">
+        <v>8357059907</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="8">
+        <v>8195300576</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="8">
+        <v>3908490120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="8">
+        <v>6654686097</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="8">
+        <v>3176554504</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="8">
+        <v>7375541777</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="8">
+        <v>2307603936</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="8">
+        <v>7539961295</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="8">
+        <v>8714929594</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="8">
+        <v>6748495954</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="8">
+        <v>5598318903</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="8">
+        <v>5366755536</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="8">
+        <v>5685425899</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="8">
+        <v>8546891943</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="8">
+        <v>7905481507</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="8">
+        <v>5681445328</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="8">
+        <v>1576469041</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="8">
+        <v>7244391357</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="8">
+        <v>5713887644</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="8">
+        <v>4360003876</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="8">
+        <v>6232183694</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="8">
+        <v>6682877186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="8">
+        <v>8911831176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="8">
+        <v>5328455783</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="8">
+        <v>4825148027</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" s="8">
+        <v>3228331930</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="8">
+        <v>7158666834</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="8">
+        <v>7998839021</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="8">
+        <v>8550635195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" s="8">
+        <v>8733465367</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="8">
+        <v>6153044829</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" s="8">
+        <v>4496254693</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="8">
+        <v>2881088394</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="8">
+        <v>3401449282</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D62" s="8">
+        <v>4405995363</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="8">
+        <v>2219599156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="8">
+        <v>3482112190</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="8">
+        <v>8411360361</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="8">
+        <v>2842414479</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="8">
+        <v>5876113945</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="8">
+        <v>4273126076</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" s="8">
+        <v>8077085042</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="8">
+        <v>8112643867</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" s="8">
+        <v>3685782386</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" s="8">
+        <v>6205596324</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="8">
+        <v>6578497608</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" s="8">
+        <v>2602080020</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="8">
+        <v>8796416295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="8">
+        <v>5978571640</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="8">
+        <v>5716170881</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="8">
+        <v>6927479136</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="8">
+        <v>8625176197</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80" s="8">
+        <v>3221738150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="8">
+        <v>2217423855</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="3">
+        <v>123</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="2"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F52A68-6E14-400A-9629-43FA86580504}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel/LookupFunctions1.xlsx
+++ b/Excel/LookupFunctions1.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184FF18E-6443-4CF5-B156-E9A564D51C53}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8FA33A-5416-47D5-8341-A8636073B955}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="3" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" firstSheet="2" activeTab="8" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
     <sheet name="Vlookup" sheetId="2" r:id="rId2"/>
     <sheet name="VData" sheetId="4" r:id="rId3"/>
     <sheet name="VResult" sheetId="5" r:id="rId4"/>
-    <sheet name="HData" sheetId="6" r:id="rId5"/>
-    <sheet name="HResult" sheetId="7" r:id="rId6"/>
-    <sheet name="Liminations" sheetId="8" r:id="rId7"/>
-    <sheet name="IndexAndMatch" sheetId="9" r:id="rId8"/>
-    <sheet name="XLookup" sheetId="10" r:id="rId9"/>
+    <sheet name="VMatch" sheetId="11" r:id="rId5"/>
+    <sheet name="HData" sheetId="6" r:id="rId6"/>
+    <sheet name="HResult" sheetId="7" r:id="rId7"/>
+    <sheet name="Liminations" sheetId="8" r:id="rId8"/>
+    <sheet name="IndexAndMatch" sheetId="9" r:id="rId9"/>
+    <sheet name="XLookup" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RawData!$A$1:$AI$85</definedName>
@@ -35,8 +36,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anudip1</author>
+  </authors>
+  <commentList>
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{1181C973-9148-4CED-A776-2C4B1F30240C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anudip1:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Getting wrong result because inserted a new column </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="425">
   <si>
     <t>S.No</t>
   </si>
@@ -1209,13 +1244,115 @@
   </si>
   <si>
     <t>Index And Match</t>
+  </si>
+  <si>
+    <t>StudentName</t>
+  </si>
+  <si>
+    <t>Attendance %</t>
+  </si>
+  <si>
+    <t>Aptitude Count</t>
+  </si>
+  <si>
+    <t>Batch Code</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>Actual Center</t>
+  </si>
+  <si>
+    <t>Center Manager</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Funder</t>
+  </si>
+  <si>
+    <t>Attendance%</t>
+  </si>
+  <si>
+    <t>Course Level Attendance%</t>
+  </si>
+  <si>
+    <t>TD Lab Marks%</t>
+  </si>
+  <si>
+    <t>TD Lab Completion%</t>
+  </si>
+  <si>
+    <t>Lab Count</t>
+  </si>
+  <si>
+    <t>Lab Assigned</t>
+  </si>
+  <si>
+    <t>MCQ Marks%</t>
+  </si>
+  <si>
+    <t>MCQ Completion%</t>
+  </si>
+  <si>
+    <t>MCQ Count</t>
+  </si>
+  <si>
+    <t>MCQ Assigned</t>
+  </si>
+  <si>
+    <t>Sprint1%</t>
+  </si>
+  <si>
+    <t>Sprint2%</t>
+  </si>
+  <si>
+    <t>iChat%</t>
+  </si>
+  <si>
+    <t>iChat Count</t>
+  </si>
+  <si>
+    <t>Aptitude%</t>
+  </si>
+  <si>
+    <t>Aptitute Completion%</t>
+  </si>
+  <si>
+    <t>Aptitude Assigned</t>
+  </si>
+  <si>
+    <t>ANP-D6211</t>
+  </si>
+  <si>
+    <t>DPBA</t>
+  </si>
+  <si>
+    <t>TSACC</t>
+  </si>
+  <si>
+    <t>Dinesh Korlana</t>
+  </si>
+  <si>
+    <t>Apr 27, 2026</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>ACCENTURE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1280,6 +1417,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -7578,6 +7728,241 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F52A68-6E14-400A-9629-43FA86580504}">
+  <dimension ref="B2:AB7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="26"/>
+    <col min="2" max="2" width="12" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.36328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.36328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.81640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" style="26" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1796875" style="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.08984375" style="26" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.6328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.453125" style="26" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.90625" style="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="8.1796875" style="26" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.453125" style="26" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.26953125" style="26" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.90625" style="26" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.7265625" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B2" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="3" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B3" s="26" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="26">
+        <v>96</v>
+      </c>
+      <c r="E3" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B6" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>396</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>398</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>400</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>401</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="N6" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>405</v>
+      </c>
+      <c r="P6" s="26" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q6" s="26" t="s">
+        <v>407</v>
+      </c>
+      <c r="R6" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="S6" s="26" t="s">
+        <v>409</v>
+      </c>
+      <c r="T6" s="26" t="s">
+        <v>410</v>
+      </c>
+      <c r="U6" s="26" t="s">
+        <v>411</v>
+      </c>
+      <c r="V6" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="W6" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="X6" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="Y6" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="Z6" s="26" t="s">
+        <v>416</v>
+      </c>
+      <c r="AA6" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="AB6" s="26" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="7" spans="2:28" x14ac:dyDescent="0.35">
+      <c r="B7" s="26" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>419</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>421</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>423</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>424</v>
+      </c>
+      <c r="K7" s="26">
+        <v>96</v>
+      </c>
+      <c r="L7" s="26">
+        <v>21</v>
+      </c>
+      <c r="M7" s="26">
+        <v>90</v>
+      </c>
+      <c r="N7" s="26">
+        <v>100</v>
+      </c>
+      <c r="O7" s="26">
+        <v>2</v>
+      </c>
+      <c r="P7" s="26">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="26">
+        <v>94</v>
+      </c>
+      <c r="R7" s="26">
+        <v>100</v>
+      </c>
+      <c r="S7" s="26">
+        <v>2</v>
+      </c>
+      <c r="T7" s="26">
+        <v>2</v>
+      </c>
+      <c r="U7" s="26">
+        <v>0</v>
+      </c>
+      <c r="V7" s="26">
+        <v>0</v>
+      </c>
+      <c r="W7" s="26">
+        <v>0</v>
+      </c>
+      <c r="X7" s="26">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="26">
+        <v>98</v>
+      </c>
+      <c r="Z7" s="26">
+        <v>100</v>
+      </c>
+      <c r="AA7" s="26">
+        <v>5</v>
+      </c>
+      <c r="AB7" s="26">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{864EEA15-3066-4C07-890E-F9E5378B34E7}">
   <dimension ref="D2:M10"/>
@@ -8052,6 +8437,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDFC545-9B15-4697-A1A4-9F000C5DD507}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28309287-5748-4475-AD32-79E6241BFE4B}">
   <dimension ref="B2:CD7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9697,7 +10091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDB9094-8273-4A0A-A89A-87F8A1046DB3}">
   <dimension ref="F7:H8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9749,7 +10143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C864E1D-F0E0-48D3-A141-473B8953EB5C}">
   <dimension ref="B1:L81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -11514,1260 +11908,1413 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCC2C67-833C-46AB-A423-5F580E3249B4}">
-  <dimension ref="A1:J85"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCCC2C67-833C-46AB-A423-5F580E3249B4}">
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.90625" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="18.90625" customWidth="1"/>
+    <col min="3" max="3" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.90625" customWidth="1"/>
+    <col min="8" max="8" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7265625" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="8">
+      <c r="E2" s="8">
         <v>6399221384</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="8">
+      <c r="D3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="8">
         <v>8732960724</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="8">
+      <c r="D4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="8">
         <v>3928683138</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="D5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="8">
         <v>6302977515</v>
       </c>
-      <c r="G5" s="7" t="str">
-        <f>INDEX($A$2:$D$81,10,2)</f>
+      <c r="H5" s="7">
+        <f>INDEX($A$2:$E$81,10,2)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="str">
+        <f>INDEX(C2:C1000,10)</f>
         <v>BURRI VINITHA</v>
       </c>
-      <c r="H5" s="8" t="str">
-        <f>INDEX(B2:B1000,10)</f>
-        <v>BURRI VINITHA</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="8">
         <v>3285643454</v>
       </c>
-      <c r="G6" s="8">
-        <f>INDEX($A$2:$D$81,10,4)</f>
+      <c r="H6" s="8" t="str">
+        <f>INDEX($A$2:$E$81,10,4)</f>
+        <v>Full Stack</v>
+      </c>
+      <c r="I6" s="8">
+        <f>INDEX($E$2:$E$81,10)</f>
         <v>1693682470</v>
       </c>
-      <c r="H6" s="8">
-        <f>INDEX($D$2:$D$81,10)</f>
-        <v>1693682470</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="8">
+      <c r="E7" s="8">
         <v>6204804746</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="8">
+      <c r="D8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="8">
         <v>8402592334</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="8">
         <v>1770577932</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="8">
+      <c r="E10" s="8">
         <v>1087593685</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="D11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="8">
         <v>1693682470</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="8">
         <v>1821308586</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="G12" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="G12" s="8">
-        <f>MATCH($F$12,$A$2:$A$82,0)</f>
+      <c r="H12" s="8">
+        <f>MATCH($G$12,$A$2:$A$82,0)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8"/>
+      <c r="C13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="D13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="8">
         <v>1683546545</v>
       </c>
-      <c r="G13" s="26"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="26"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="8">
         <v>5506439807</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8"/>
+      <c r="C15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="8">
+      <c r="E15" s="8">
         <v>3565997600</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="8">
         <v>2685014153</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="8">
         <v>8144007188</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="8">
+      <c r="E18" s="8">
         <v>5451418853</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H18" s="26" t="str">
-        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),2)</f>
+      <c r="I18" s="26">
+        <f>INDEX($A$2:$E$82,MATCH($H$18,$A$2:$A$82,0),2)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="8" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H$18,$A$2:$A$82,0),3)</f>
         <v>K. SANTOSHI</v>
       </c>
-      <c r="I18" s="8" t="str">
-        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),3)</f>
+      <c r="K18" s="8" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H$18,$A$2:$A$82,0),4)</f>
         <v>Full Stack</v>
       </c>
-      <c r="J18" s="8">
-        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),4)</f>
-        <v>1359937879</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="8">
+      <c r="D19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="8">
         <v>2352093828</v>
       </c>
-      <c r="H19" s="36" t="str">
-        <f>INDEX($A$2:$D$82,MATCH($G$18,$A$2:$A$82,0),MATCH($H$17,$A$1:$D$1,0))</f>
+      <c r="I19" s="36" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H$18,$A$2:$A$82,0),MATCH($I$17,$A$1:$E$1,0))</f>
         <v>K. SANTOSHI</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8"/>
+      <c r="C20" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="D20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="8">
         <v>4851546652</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="8">
+      <c r="E21" s="8">
         <v>6604423032</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8"/>
+      <c r="C22" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="8">
+      <c r="E22" s="8">
         <v>4267924443</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H22" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8"/>
+      <c r="C23" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="8">
         <v>2776428499</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8"/>
+      <c r="C24" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="8">
+      <c r="D24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="8">
         <v>2344591250</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H24" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I24" s="26">
+        <f>INDEX($A$2:$E$82,MATCH($H$24,$A$2:$A$82,0),2)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H$24,$A$2:$A$82,0),3)</f>
+        <v>SHOAIB AKHTAR</v>
+      </c>
+      <c r="K24" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H$24,$A$2:$A$82,0),4)</f>
+        <v>Full Stack</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8"/>
+      <c r="C25" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="8">
+      <c r="D25" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="8">
         <v>4564000793</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H25" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I25" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H25,$A$2:$A$82,0),MATCH(I$23,$A$1:$E$1,0))</f>
+        <v>SHOAIB AKHTAR</v>
+      </c>
+      <c r="J25" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H25,$A$2:$A$82,0),MATCH(J$23,$A$1:$E$1,0))</f>
+        <v>Full Stack</v>
+      </c>
+      <c r="K25" s="26">
+        <f>INDEX($A$2:$E$82,MATCH($H25,$A$2:$A$82,0),MATCH(K$23,$A$1:$E$1,0))</f>
+        <v>7998839021</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8"/>
+      <c r="C26" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="D26" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="8">
         <v>7831800139</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H26" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I26" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H26,$A$2:$A$82,0),MATCH(I$23,$A$1:$E$1,0))</f>
+        <v>M. BALAJI</v>
+      </c>
+      <c r="J26" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H26,$A$2:$A$82,0),MATCH(J$23,$A$1:$E$1,0))</f>
+        <v>ITES</v>
+      </c>
+      <c r="K26" s="26">
+        <f>INDEX($A$2:$E$82,MATCH($H26,$A$2:$A$82,0),MATCH(K$23,$A$1:$E$1,0))</f>
+        <v>7375541777</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8"/>
+      <c r="C27" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="8">
+      <c r="D27" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="8">
         <v>1359937879</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H27" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H27,$A$2:$A$82,0),MATCH(I$23,$A$1:$E$1,0))</f>
+        <v>GARAPATI GAYATHRI</v>
+      </c>
+      <c r="J27" s="26" t="str">
+        <f>INDEX($A$2:$E$82,MATCH($H27,$A$2:$A$82,0),MATCH(J$23,$A$1:$E$1,0))</f>
+        <v>ITES</v>
+      </c>
+      <c r="K27" s="26">
+        <f>INDEX($A$2:$E$82,MATCH($H27,$A$2:$A$82,0),MATCH(K$23,$A$1:$E$1,0))</f>
+        <v>4267924443</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8"/>
+      <c r="C28" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="8">
+      <c r="E28" s="8">
         <v>8357059907</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8"/>
+      <c r="C29" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="8">
+      <c r="D29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="8">
         <v>8195300576</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8"/>
+      <c r="C30" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="8">
+      <c r="D30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="8">
         <v>3908490120</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8"/>
+      <c r="C31" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="8">
+      <c r="D31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="8">
         <v>6654686097</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8"/>
+      <c r="C32" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="8">
+      <c r="D32" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="8">
         <v>3176554504</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8"/>
+      <c r="C33" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="D33" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="8">
+      <c r="E33" s="8">
         <v>7375541777</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8"/>
+      <c r="C34" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D34" s="8">
+      <c r="E34" s="8">
         <v>2307603936</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8"/>
+      <c r="C35" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D35" s="8">
+      <c r="D35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="8">
         <v>7539961295</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8"/>
+      <c r="C36" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="8">
+      <c r="D36" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="8">
         <v>8714929594</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8"/>
+      <c r="C37" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="D37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="8">
+      <c r="E37" s="8">
         <v>6748495954</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8"/>
+      <c r="C38" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="8">
+      <c r="D38" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="8">
         <v>5598318903</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8"/>
+      <c r="C39" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="8">
+      <c r="D39" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="8">
         <v>5366755536</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8"/>
+      <c r="C40" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="D40" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="8">
+      <c r="E40" s="8">
         <v>5685425899</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8"/>
+      <c r="C41" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="D41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="8">
+      <c r="E41" s="8">
         <v>8546891943</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8"/>
+      <c r="C42" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="D42" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="8">
+      <c r="E42" s="8">
         <v>7905481507</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8"/>
+      <c r="C43" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="D43" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="8">
+      <c r="E43" s="8">
         <v>5681445328</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="8"/>
+      <c r="C44" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="8">
+      <c r="D44" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="8">
         <v>1576469041</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="8"/>
+      <c r="C45" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C45" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D45" s="8">
+      <c r="D45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="8">
         <v>7244391357</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="8"/>
+      <c r="C46" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="8">
+      <c r="D46" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="8">
         <v>5713887644</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8"/>
+      <c r="C47" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="D47" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="8">
+      <c r="E47" s="8">
         <v>4360003876</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="8"/>
+      <c r="C48" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" s="8">
+      <c r="D48" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="8">
         <v>6232183694</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="8"/>
+      <c r="C49" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D49" s="8">
+      <c r="D49" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="8">
         <v>6682877186</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="8"/>
+      <c r="C50" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="D50" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D50" s="8">
+      <c r="E50" s="8">
         <v>8911831176</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="8"/>
+      <c r="C51" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D51" s="8">
+      <c r="D51" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="8">
         <v>5328455783</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="8"/>
+      <c r="C52" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="D52" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D52" s="8">
+      <c r="E52" s="8">
         <v>4825148027</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="8"/>
+      <c r="C53" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D53" s="8">
+      <c r="D53" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="8">
         <v>3228331930</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="8"/>
+      <c r="C54" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54" s="8">
+      <c r="D54" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="8">
         <v>7158666834</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="8"/>
+      <c r="C55" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D55" s="8">
+      <c r="D55" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="8">
         <v>7998839021</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="8"/>
+      <c r="C56" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D56" s="8">
+      <c r="D56" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="8">
         <v>8550635195</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="8"/>
+      <c r="C57" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D57" s="8">
+      <c r="D57" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="8">
         <v>8733465367</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="8"/>
+      <c r="C58" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="D58" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D58" s="8">
+      <c r="E58" s="8">
         <v>6153044829</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="8"/>
+      <c r="C59" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="8">
+      <c r="D59" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="8">
         <v>4496254693</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="8"/>
+      <c r="C60" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60" s="8">
+      <c r="D60" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="8">
         <v>2881088394</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="8"/>
+      <c r="C61" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="D61" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="8">
+      <c r="E61" s="8">
         <v>3401449282</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="8"/>
+      <c r="C62" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D62" s="8">
+      <c r="D62" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="8">
         <v>4405995363</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="8"/>
+      <c r="C63" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="C63" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="8">
+      <c r="D63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="8">
         <v>2219599156</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="8"/>
+      <c r="C64" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="D64" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D64" s="8">
+      <c r="E64" s="8">
         <v>3482112190</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="8"/>
+      <c r="C65" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="8">
+      <c r="D65" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="8">
         <v>8411360361</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="8"/>
+      <c r="C66" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="D66" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="8">
+      <c r="E66" s="8">
         <v>2842414479</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="8"/>
+      <c r="C67" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C67" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D67" s="8">
+      <c r="D67" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="8">
         <v>5876113945</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="8"/>
+      <c r="C68" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D68" s="8">
+      <c r="D68" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="8">
         <v>4273126076</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="8"/>
+      <c r="C69" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D69" s="8">
+      <c r="D69" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="8">
         <v>8077085042</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="8"/>
+      <c r="C70" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="D70" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="8">
+      <c r="E70" s="8">
         <v>8112643867</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="8"/>
+      <c r="C71" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C71" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D71" s="8">
+      <c r="D71" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="8">
         <v>3685782386</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="8"/>
+      <c r="C72" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="C72" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D72" s="8">
+      <c r="D72" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="8">
         <v>6205596324</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="8"/>
+      <c r="C73" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="D73" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="8">
+      <c r="E73" s="8">
         <v>6578497608</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="8"/>
+      <c r="C74" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D74" s="8">
+      <c r="D74" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="8">
         <v>2602080020</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="8"/>
+      <c r="C75" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="D75" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="8">
+      <c r="E75" s="8">
         <v>8796416295</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="8"/>
+      <c r="C76" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="D76" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D76" s="8">
+      <c r="E76" s="8">
         <v>5978571640</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="8"/>
+      <c r="C77" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="C77" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D77" s="8">
+      <c r="D77" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="8">
         <v>5716170881</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="8"/>
+      <c r="C78" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="C78" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D78" s="8">
+      <c r="D78" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="8">
         <v>6927479136</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="8"/>
+      <c r="C79" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="C79" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D79" s="8">
+      <c r="D79" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="8">
         <v>8625176197</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="8"/>
+      <c r="C80" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D80" s="8">
+      <c r="D80" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="8">
         <v>3221738150</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="8"/>
+      <c r="C81" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="C81" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D81" s="8">
+      <c r="D81" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81" s="8">
         <v>2217423855</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>123</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="2"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D82" s="3"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="2"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D83" s="3"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="2"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D84" s="3"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="2"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18F52A68-6E14-400A-9629-43FA86580504}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/LookupFunctions1.xlsx
+++ b/Excel/LookupFunctions1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8FA33A-5416-47D5-8341-A8636073B955}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15CB530-107D-4D6A-A95B-40247B6FB616}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" firstSheet="2" activeTab="8" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" firstSheet="2" activeTab="9" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="N3" s="8" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,3),"P","A","L")</f>
-        <v>L</v>
+        <v>A</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
@@ -12400,15 +12400,15 @@
         <v>229</v>
       </c>
       <c r="I25" s="26" t="str">
-        <f>INDEX($A$2:$E$82,MATCH($H25,$A$2:$A$82,0),MATCH(I$23,$A$1:$E$1,0))</f>
+        <f t="shared" ref="I25:K27" si="0">INDEX($A$2:$E$82,MATCH($H25,$A$2:$A$82,0),MATCH(I$23,$A$1:$E$1,0))</f>
         <v>SHOAIB AKHTAR</v>
       </c>
       <c r="J25" s="26" t="str">
-        <f>INDEX($A$2:$E$82,MATCH($H25,$A$2:$A$82,0),MATCH(J$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>Full Stack</v>
       </c>
       <c r="K25" s="26">
-        <f>INDEX($A$2:$E$82,MATCH($H25,$A$2:$A$82,0),MATCH(K$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>7998839021</v>
       </c>
     </row>
@@ -12430,15 +12430,15 @@
         <v>143</v>
       </c>
       <c r="I26" s="26" t="str">
-        <f>INDEX($A$2:$E$82,MATCH($H26,$A$2:$A$82,0),MATCH(I$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>M. BALAJI</v>
       </c>
       <c r="J26" s="26" t="str">
-        <f>INDEX($A$2:$E$82,MATCH($H26,$A$2:$A$82,0),MATCH(J$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>ITES</v>
       </c>
       <c r="K26" s="26">
-        <f>INDEX($A$2:$E$82,MATCH($H26,$A$2:$A$82,0),MATCH(K$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>7375541777</v>
       </c>
     </row>
@@ -12460,15 +12460,15 @@
         <v>99</v>
       </c>
       <c r="I27" s="26" t="str">
-        <f>INDEX($A$2:$E$82,MATCH($H27,$A$2:$A$82,0),MATCH(I$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>GARAPATI GAYATHRI</v>
       </c>
       <c r="J27" s="26" t="str">
-        <f>INDEX($A$2:$E$82,MATCH($H27,$A$2:$A$82,0),MATCH(J$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>ITES</v>
       </c>
       <c r="K27" s="26">
-        <f>INDEX($A$2:$E$82,MATCH($H27,$A$2:$A$82,0),MATCH(K$23,$A$1:$E$1,0))</f>
+        <f t="shared" si="0"/>
         <v>4267924443</v>
       </c>
     </row>

--- a/Excel/LookupFunctions1.xlsx
+++ b/Excel/LookupFunctions1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15CB530-107D-4D6A-A95B-40247B6FB616}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29051891-10F5-4927-81CF-5D5833776504}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" firstSheet="2" activeTab="9" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="2" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RawData!$A$1:$AI$85</definedName>
+    <definedName name="StudentCode">VData!$A$2:$A$26</definedName>
+    <definedName name="StudentData">VData!$A$2:$C$26</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -8428,8 +8430,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="5:7" x14ac:dyDescent="0.35">
-      <c r="F7" s="20"/>
+    <row r="7" spans="5:7" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F7" s="20" t="str">
+        <f>UPPER(VLOOKUP(E6,StudentData,2,FALSE))</f>
+        <v>KANCHARL A ASHWINI</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/LookupFunctions1.xlsx
+++ b/Excel/LookupFunctions1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29051891-10F5-4927-81CF-5D5833776504}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDAC9DA-7EEC-49F7-BF1A-3677F06B549C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="2" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="1" xr2:uid="{283383FA-06D3-45BA-9C1B-BAA55A9A2CC4}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="N3" s="8" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,3),"P","A","L")</f>
-        <v>A</v>
+        <v>L</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="8"/>
@@ -7638,7 +7638,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Select Form the DropDown" error="Select Form the DropDown" sqref="M2:AI81" xr:uid="{3B9CC5D6-AEB5-4F22-AC8C-FF10F3850228}">
       <formula1>"P,A,L"</formula1>
     </dataValidation>
@@ -8026,11 +8026,11 @@
     </row>
     <row r="6" spans="4:13" s="20" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D6" s="8" t="s">
-        <v>197</v>
+        <v>12</v>
       </c>
       <c r="E6" s="8" t="str">
         <f>VLOOKUP($D$6,RawData!$C$2:$H$82,2,FALSE)</f>
-        <v>R. VIGNESH</v>
+        <v>NIKITHA ADULA</v>
       </c>
       <c r="F6" s="8" t="str">
         <f>VLOOKUP($D$6,RawData!$C$2:$H$82,3,FALSE)</f>
@@ -8038,15 +8038,15 @@
       </c>
       <c r="G6" s="8">
         <f>VLOOKUP($D$6,RawData!$C$2:$H$82,4,FALSE)</f>
-        <v>4360003876</v>
+        <v>6399221384</v>
       </c>
       <c r="H6" s="8" t="str">
         <f>VLOOKUP($D$6,RawData!$C$2:$H$82,5,FALSE)</f>
-        <v>rvignesh.itesites@gmail.com</v>
+        <v>nikitha.itesites@gmail.com</v>
       </c>
       <c r="I6" s="8" t="str">
         <f>VLOOKUP($D$6,RawData!$C$2:$H$82,6,FALSE)</f>
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
